--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:18</t>
+    <t xml:space="preserve">2026-09-09 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:13</t>
+    <t xml:space="preserve">2026-09-17 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:09</t>
+    <t xml:space="preserve">2026-09-23 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:38</t>
+    <t xml:space="preserve">2026-10-02 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Laja</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:19</t>
+    <t xml:space="preserve">2026-10-04 09:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:05</t>
+    <t xml:space="preserve">2026-10-05 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -597,7 +597,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>506876.62</v>
+        <v>506876.63</v>
       </c>
     </row>
     <row r="4">
@@ -920,7 +920,7 @@
         <v>2024</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>302441.12</v>
+        <v>302441.13</v>
       </c>
     </row>
     <row r="23">
